--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -474,9 +474,17 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>🎭🔀 The Register Role-Caller: The 47th member of The Council</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -959,15 +967,15 @@
       <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="C27" t="n">
-        <v>56</v>
+      <c r="B27" t="n">
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -975,15 +983,15 @@
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="C28" t="n">
-        <v>56</v>
+      <c r="B28" t="n">
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1055,15 +1063,15 @@
       <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="C33" t="n">
-        <v>56</v>
+      <c r="B33" t="n">
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1071,15 +1079,15 @@
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="C34" t="n">
-        <v>56</v>
+      <c r="B34" t="n">
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -967,15 +967,15 @@
       <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
-        <v>7</v>
+      <c r="C27" t="n">
+        <v>70</v>
       </c>
       <c r="E27" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -983,15 +983,15 @@
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
-        <v>7</v>
+      <c r="C28" t="n">
+        <v>72</v>
       </c>
       <c r="E28" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1063,15 +1063,15 @@
       <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
-        <v>8</v>
+      <c r="C33" t="n">
+        <v>71</v>
       </c>
       <c r="E33" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1079,15 +1079,15 @@
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
-        <v>8</v>
+      <c r="C34" t="n">
+        <v>73</v>
       </c>
       <c r="E34" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, reported): the lock is HAIR and must swing, so it continues onto the skin's own front lock (Bangs 3 -&gt; 5 -&gt; 7) and clamps at its end, rather than onto the chest. The earlier review asked which bone drives the SKIN at that height and answered Body:56 -- the torso bone, 2715 of the skin's vertices deep -- so the lock could not move and hung rigid through the arms. The skin's lock stops at y 1.241 and Citlali's runs on to 1.037, so there is no counterpart for the lower half and the chain's end takes it. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -975,7 +975,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -975,7 +975,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05: the reported clipping was NOT this row. These braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose and the skin holds its arms differently, so the arm is drawn THROUGH them -- an intersection, which no bone choice can fix (all three tried looked identical). It is fixed by GIMIComponentFixerConfig::Component::pushAway, 2 cm forward, one entry a side. The target below is still the right carrier for how the braid MOVES. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>227 verts (Head) -&gt; 550 verts (A), dist 0.0156; runner-up Eyes:0 at dist 0.0330</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 227 verts (Head) -&gt; 550 verts (A), dist 0.0156; runner-up Eyes:0 at dist 0.0330</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>353 verts (Body/Head) -&gt; 344 verts (A), dist 0.0496; runner-up Bangs:7 at dist 0.0538</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 353 verts (Body/Head) -&gt; 344 verts (A), dist 0.0496; runner-up Bangs:7 at dist 0.0538</t>
         </is>
       </c>
     </row>
@@ -967,15 +967,15 @@
       <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="C27" t="n">
-        <v>70</v>
+      <c r="B27" t="n">
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>0.3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -983,15 +983,15 @@
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="C28" t="n">
-        <v>72</v>
+      <c r="B28" t="n">
+        <v>7</v>
       </c>
       <c r="E28" t="n">
         <v>0.3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>129 verts (Head) -&gt; 493 verts (A), dist 0.0097; runner-up Bangs:6 at dist 0.0712</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 129 verts (Head) -&gt; 493 verts (A), dist 0.0097; runner-up Bangs:6 at dist 0.0712</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>351 verts (Body/Head) -&gt; 407 verts (A), dist 0.0504; runner-up Bangs:8 at dist 0.0511</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 351 verts (Body/Head) -&gt; 407 verts (A), dist 0.0504; runner-up Bangs:8 at dist 0.0511</t>
         </is>
       </c>
     </row>
@@ -1063,15 +1063,15 @@
       <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="C33" t="n">
-        <v>71</v>
+      <c r="B33" t="n">
+        <v>8</v>
       </c>
       <c r="E33" t="n">
         <v>0.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1079,15 +1079,15 @@
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="C34" t="n">
-        <v>73</v>
+      <c r="B34" t="n">
+        <v>8</v>
       </c>
       <c r="E34" t="n">
         <v>0.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): the reported clipping was NOT this row, and NO row can fix it. The skinning matrix is pose*bindInverse, i.e. the IDENTITY at the character's own rest pose, so a remapped mod renders at Citlali's coordinates whatever bone it is bound to -- rebinding these braids live to Body:56, Body:9/33, Body:57/58 and Body:70-73 and reloading between each gives four PIXEL-MATCHED pictures. The braids pass the upper arm with 6.8 mm to spare in Citlali's own bind pose; on her own model her hair-PHYSICS bones swing them clear, and the skin has no bone that animates there, so they stay in the groove between arm and chest and the arm sweeps through. Fixed by GIMIComponentFixerConfig::Component::pushAway: 3 cm away from the MIDLINE point (0, 1.13, -0.10), i.e. mostly forward and partly OUTWARD. (2 cm straight forward shipped first and drew a second user report -- it lays the braid on the BUST.) Checked against the same mod unfixed on Citlali herself, via the outfit shop's Dawnseer card: her braids hang OUTBOARD, clear of both arm and chest -- see AI Agent Help/CreatingRemaps/Images/Citlali/CitlaliWhisperBraidAgainstCitlali.png. The target below is kept as the best answer to how the braid would MOVE, but it is NOT what fixed anything, and its DEPTH is poor: the dress links sit at z 0.126/0.152 against the braid's 0.03, a 10 cm lever in the axis nobody checked. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 227 verts (Head) -&gt; 550 verts (A), dist 0.0156; runner-up Eyes:0 at dist 0.0330</t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 353 verts (Body/Head) -&gt; 344 verts (A), dist 0.0496; runner-up Bangs:7 at dist 0.0538</t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 129 verts (Head) -&gt; 493 verts (A), dist 0.0097; runner-up Bangs:6 at dist 0.0712</t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. 351 verts (Body/Head) -&gt; 407 verts (A), dist 0.0504; runner-up Bangs:8 at dist 0.0511</t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32), and the row used to CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body. One braid in two index spaces on two unrelated bones, which is the whole of three user reports: it could not flow (the lower links rode a Body bone and no Body bone animates there), and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam and stood forward of the hair it grows out of. ONE part belongs on ONE component's bones -- the rule Neuvillette's torn capes already wrote down. All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The amplitude objection to that chain is real and is answered in the FIXER, not by another bone: bone 7's lever is 3.8 cm and Citlali's braid hangs 24 cm below it, so GIMIComponentFixerConfig::Component::splitGroups shares each lower link's weight with the Bangs' head bone in the ratio of the levers (0.35 for 25, 0.20 for 26). Note for the next reviewer: the three Body bones tried here -- 56, the clavicle, the dress chain 70-&gt;72 -- render IDENTICALLY, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 4 cm pushAway clears now that the braid is whole. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway clears now that the braid is whole (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="10"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,11 +71,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -481,10 +487,18 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>🪞⚖️ The Mirror Breaker: The 61st member of The Council</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -943,7 +957,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -959,7 +973,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -975,7 +989,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -991,7 +1005,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1053,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1055,7 +1069,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1071,7 +1085,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1101,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (symmetric: the mod's two braids are mirror-exact to 0.0000 in z, so the lean that made one side clip first belongs to the skin's standing idle, and a per-side value would be tuned to one animation). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a 6.5 cm pushAway over the LOWER TWO links of each braid clears now that the braid is whole (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: 9.6 cm on her LEFT against 6.5 on her right. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock below the skin's side locks (24-26 hangs to chest height): the chest drives that skin (vertices mode 52%); the chain's Body:3 is the shoulder and would swing the lock with the arm. Tool proposed Body:3 [650 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0768; runner-up Body:56 at dist 0.1048; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: front hair lock end on the chest (vertices mode 67%); not the arm bone Body:4. Tool proposed Body:4 [616 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:57 at dist 0.0696; in chain 25-26 -&gt; Body:3-4]</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 25: front hair lock onto the chest (vertices mode 52%). Tool proposed Body:5 [646 verts (Body/Head) -&gt; 393 verts (A/B), dist 0.0769; runner-up Body:58 at dist 0.0627; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 6 cm sideways and 9 forward on her left and 4 and 6 on her right. Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. Reviewed 2026-10-04 (IN GAME, two rounds): the lock goes on the skin's front-hanging DRESS chain Body 70-&gt;72 (mirror 71-&gt;73), whose links sit at y 1.189 and 1.095 against this lock's 1.171 and 1.095 -- pivots at the part's own HEIGHT, so the lever is nearly zero. Two earlier answers failed: Body:56 (the torso bone) could not move at all and the lock hung rigid through the arms, and continuing the chain onto the skin's own front lock (Bangs 3-&gt;5-&gt;7) put the tip 19 cm below its pivot, which a few degrees of hair sim threw INTO the arm -- the hair clears the arm by 6.8 mm at the bind pose. Rank by lever first, then by whether the carrier moves the same way, then material. Previously: Reviewed: mirror of 26: front hair lock end onto the chest (vertices mode 67%). Tool proposed Body:6 [612 verts (Body/Head) -&gt; 256 verts (A/B), dist 0.0902; runner-up Body:60 at dist 0.1103; in chain 31-32 -&gt; Body:5-6]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/CitlaliRemapDraft.xlsx
+++ b/Data/RemapDrafts/CitlaliRemapDraft.xlsx
@@ -950,14 +950,14 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0.342</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still.  NOTE 2026-10-06: this link is the lock's ROOT and now rides the Bangs HEAD bone (0), not the skin's front-lock root (3/4). It owns y 1.34-1.42 outright and 56% of 1.30-1.34 -- the stretch where the braid is SANDWICHED, 4 mm from the fringe in front and touching the loose hair behind. On Citlali all three hang off one skeleton and move together; here the braid rode the lock chain, the fringe its own bone and the loose hair the Body back-hair chains (108-115), so a third independent motion closed a gap no displacement can clear from both sides. The swing starts at 24 -&gt; 5 instead, and the source weights blend 23 into 24 so the handover is a gradient. NOT the 2026-10-04 damping, which shared the LOWER links' weight and left the braid rigid -- only the root moves to the head.</t>
         </is>
       </c>
     </row>
@@ -1046,14 +1046,14 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0.425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still. </t>
+          <t>NOTE 2026-10-05 (settled, after five user reports): this link is part of a FOUR-LINK front lock (23-&gt;24-&gt;25-&gt;26, mirror 29-&gt;30-&gt;31-&gt;32). The row's own fault was that it CUT that chain across two components -- 23/24 and 29/30 to the Bangs, 25/26 and 31/32 to the Body -- so one braid was skinned in two index spaces by two unrelated bones: it could not flow (the lower links rode a Body bone where nothing animates) and a VGPushAway added to clear the arm moved only the half configured on that component, so the braid broke at the seam. ONE part belongs on ONE component's bones (the Neuvillette lesson). All four links now go to the skin's own front lock, Bangs 3-&gt;5-&gt;7 (mirror 4-&gt;6-&gt;8). The two faults that remained were in the FIXER, not in this table, and the next reviewer should not try to fix them here: a splitGroups damping that made the braid rigid with the head (removed -- a longer lock swinging further at the tip is what hair does), and a clip through the shoulder that a pushAway over the LOWER TWO links of each braid clears now that the braid is whole -- OUT and forward, about 4.7 cm sideways and 10.1 forward on her left and 4.1 and 6.3 on her right -- a FLOOR rather than a preference, because coming back inside |x| 0.105 puts a braid in front of the bust again, where it needs ~12 cm of forward travel to clear and reads as detached (her left had room for 1.4 cm; her right is already at its minimum, losing its margin at x +0.097, y 1.15). Going SIDEWAYS is what did the work, and the reason generalises: a body is much shallower just outside the bust than in front of it (on this mod's own body at y 1.10-1.14 the front surface is z 0.124-0.149 inside |x| 0.10 and z 0.015-0.026 outside it), so the first 3 cm of lateral travel carries the braid off the breast and buys ~10 cm of clearance where forward travel only buys its own length. An almost purely forward push cleared by 0.4 cm at best and the idle kept closing it, which is what three user reports were about; angled out it clears by 3.5-10 cm in every band (naming all four links reached the hairline and moved her BANGS forward 2.5-4.6 cm; naming 25/26 and 31/32 moves nothing above y 1.356) (PER SIDE, 2026-10-05: the larger distance on her LEFT. It shipped symmetric twice on an argument made entirely from the files -- the mod's two braids are mirror-exact to 0.0000 in z and their share profiles agree band for band, and the skin's bones 7 and 8 are a mirror PAIR (centroids -0.059/+0.063, same y 1.279, same 1.241-1.379 span) -- and the user still reported the left braid clipping three times. MIRROR-EXACT INPUTS DO NOT GIVE A MIRROR-EXACT PICTURE: the difference is in the skin's standing idle, which no file here can see. The usual objection, that a per-side value is tuned to the animation it was measured in, costs nothing here -- the skin cannot be worn without owning the character, so the shop preview's idle is the only pose it is ever seen in). Known and not fixable from this table or the fixer: when she BENDS, both braids pass through her chest -- the skin has no hair bone below y 1.24, so the whole braid hangs off a head-parented chain and the torso rotates into it. For the record: the Body carriers tried for the lower half -- 56, the clavicle 9/33, the shoulder cloth 57/58, the dress chain 70-&gt;72 -- render IDENTICALLY when rebound live, because a skinning matrix is the identity at the rest pose. Judge a carrier on an idle SERIES, never on a still.  NOTE 2026-10-06: this link is the lock's ROOT and now rides the Bangs HEAD bone (0), not the skin's front-lock root (3/4). It owns y 1.34-1.42 outright and 56% of 1.30-1.34 -- the stretch where the braid is SANDWICHED, 4 mm from the fringe in front and touching the loose hair behind. On Citlali all three hang off one skeleton and move together; here the braid rode the lock chain, the fringe its own bone and the loose hair the Body back-hair chains (108-115), so a third independent motion closed a gap no displacement can clear from both sides. The swing starts at 24 -&gt; 5 instead, and the source weights blend 23 into 24 so the handover is a gradient. NOT the 2026-10-04 damping, which shared the LOWER links' weight and left the braid rigid -- only the root moves to the head.</t>
         </is>
       </c>
     </row>
